--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.52.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.52.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.52" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.52" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.52.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.52.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0052.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0052.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -863,7 +863,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.52.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.52.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.52" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.52" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œscribed by you, and that you know the contents thereof,</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: ； but</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: following form:â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]45</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]45</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 45</t>
@@ -618,13 +622,13 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L38: symbol-only separator/garbage line :: 1842.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]45</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L71: punctuation artifact: double/multiple hyphen :: Â« The Defendant C--------D------on the</t>
+          <t>L71: punctuation artifact: double/multiple hyphen :: « The Defendant C--------D------on the</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,14 +664,10 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œThe Defendant C â€”</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: shall run thus:â€”</t>
-        </is>
-      </c>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: ； but</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -677,13 +677,13 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L40: symbol-only separator/garbage line :: 114.</t>
+          <t>L38: symbol-only separator/garbage line :: 1842.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L75: punctuation artifact: double/multiple hyphen :: Â« --------in the year of our Lord, &amp;c., appeared before</t>
+          <t>L75: punctuation artifact: double/multiple hyphen :: « --------in the year of our Lord, &amp;c., appeared before</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -717,16 +717,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” D â€”</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Â« The Defendant C ---------Dâ€” - not being able to read in case of an</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -736,13 +728,13 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L56: symbol-only separator/garbage line :: 1837.</t>
+          <t>L40: symbol-only separator/garbage line :: 114.</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L77: punctuation artifact: double/multiple hyphen :: Â« me at my chambers in the -----------of --------in the</t>
+          <t>L77: punctuation artifact: double/multiple hyphen :: « me at my chambers in the -----------of --------in the</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -762,12 +754,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -776,11 +768,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” on the-</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
@@ -791,13 +779,13 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L57: symbol-only separator/garbage line :: 24.</t>
+          <t>L56: symbol-only separator/garbage line :: 1837.</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L79: punctuation artifact: double/multiple hyphen :: Â« District of ------and answered that he had read the</t>
+          <t>L79: punctuation artifact: double/multiple hyphen :: « District of ------and answered that he had read the</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -831,11 +819,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of Form of Jurat.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
@@ -844,11 +828,15 @@
           <t>L38: symbol-only separator/garbage line :: 1837.</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L57: symbol-only separator/garbage line :: 24.</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Â« The Defendant C ---------Dâ€” - not being able to read in case of an</t>
+          <t>L93: punctuation artifact: double/multiple hyphen :: « The Defendant C ---------D— - not being able to read in case of an</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -882,11 +870,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -899,7 +883,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L95: punctuation artifact: double/multiple hyphen :: Â« or write, E ---F -----, Solicitor for the said Defendant, illiterate per-</t>
+          <t>L95: punctuation artifact: double/multiple hyphen :: « or write, E ---F -----, Solicitor for the said Defendant, illiterate per-</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -933,24 +917,20 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œforegoing answer, and signed the same in my presence,</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: - D</t>
+          <t>L63: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L98: punctuation artifact: double/multiple hyphen :: Â« contents of this answer to the said C----D-------and</t>
+          <t>L98: punctuation artifact: double/multiple hyphen :: « contents of this answer to the said C----D-------and</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -984,24 +964,20 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œand thereupon was sworn (or affirmed) before me that</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: D</t>
+          <t>L90: isolated marker/symbol line :: - D</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L102: punctuation artifact: double/multiple hyphen :: Â« and the said C-----D-------was thereupon sworn that</t>
+          <t>L102: punctuation artifact: double/multiple hyphen :: « and the said C-----D-------was thereupon sworn that</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1021,12 +997,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1035,15 +1011,15 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œThe Defendant C</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L103: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1069,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1078,11 +1054,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œcontents of this answer to the said CD â€” and</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
@@ -1107,12 +1079,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1121,11 +1093,7 @@
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthat he appeared perfectly to understand the same:</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
